--- a/exports/Current_Previous_Year_PU_Demand_Analysis.xlsx
+++ b/exports/Current_Previous_Year_PU_Demand_Analysis.xlsx
@@ -483,7 +483,7 @@
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
@@ -495,7 +495,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Demand SMH Wise - AUG 2026 | uploaded 2026-09-05T18:02:11+05:30</t>
+          <t>Demand SMH Wise - AUG 2026 | uploaded 2026-09-11T10:57:00+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -546,9 +546,7 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>A
-OBA
-BG_ISL 2026-27</t>
+          <t>A\nOBA/RG\nRG if available, else BG_ISL 2026-27</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
@@ -1282,7 +1280,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
@@ -1294,7 +1292,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PU Staff Current Year - AUG 2026 | uploaded 2026-09-05T18:02:11+05:30</t>
+          <t>PU Staff Current Year - AUG 2026 | uploaded 2026-09-11T10:57:00+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -1337,9 +1335,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>A
-OBA
-BG_ISL 2026-27</t>
+          <t>A\nOBA/RG\nRG if available, else BG_ISL 2026-27</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -2529,7 +2525,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
@@ -2541,7 +2537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PU Non Staff Current Year - AUG 2026 | uploaded 2026-09-05T18:02:11+05:30</t>
+          <t>PU Non Staff Current Year - AUG 2026 | uploaded 2026-09-11T10:57:00+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -2584,9 +2580,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>A
-OBA
-BG_ISL 2026-27</t>
+          <t>A\nOBA/RG\nRG if available, else BG_ISL 2026-27</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -3779,7 +3773,7 @@
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
@@ -3791,7 +3785,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PU Previous Year Comparison - AUG 2026 | uploaded 2026-09-05T18:02:11+05:30</t>
+          <t>PU Previous Year Comparison - AUG 2026 | uploaded 2026-09-11T10:57:00+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -3864,9 +3858,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>D
-Current OBA
-BG_ISL 2026-27</t>
+          <t>D\nCurrent OBA/RG\nRG if available, else BG_ISL 2026-27</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
@@ -6987,7 +6979,7 @@
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
@@ -6999,7 +6991,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Demand Previous Year Comparison - AUG 2026 | uploaded 2026-09-05T18:02:11+05:30</t>
+          <t>Demand Previous Year Comparison - AUG 2026 | uploaded 2026-09-11T10:57:00+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -7080,9 +7072,7 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>D
-Current OBA
-BG_ISL 2026-27</t>
+          <t>D\nCurrent OBA/RG\nRG if available, else BG_ISL 2026-27</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">

--- a/exports/Current_Previous_Year_PU_Demand_Analysis.xlsx
+++ b/exports/Current_Previous_Year_PU_Demand_Analysis.xlsx
@@ -495,7 +495,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Demand SMH Wise - AUG 2026 | uploaded 2026-09-11T10:57:00+05:30</t>
+          <t>Demand SMH Wise - AUG 2026 | uploaded 2026-09-15T16:03:44+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -1292,7 +1292,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PU Staff Current Year - AUG 2026 | uploaded 2026-09-11T10:57:00+05:30</t>
+          <t>PU Staff Current Year - AUG 2026 | uploaded 2026-09-15T16:03:44+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -2537,7 +2537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PU Non Staff Current Year - AUG 2026 | uploaded 2026-09-11T10:57:00+05:30</t>
+          <t>PU Non Staff Current Year - AUG 2026 | uploaded 2026-09-15T16:03:44+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -3785,7 +3785,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PU Previous Year Comparison - AUG 2026 | uploaded 2026-09-11T10:57:00+05:30</t>
+          <t>PU Previous Year Comparison - AUG 2026 | uploaded 2026-09-15T16:03:44+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -6991,7 +6991,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Demand Previous Year Comparison - AUG 2026 | uploaded 2026-09-11T10:57:00+05:30</t>
+          <t>Demand Previous Year Comparison - AUG 2026 | uploaded 2026-09-15T16:03:44+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>

--- a/exports/Current_Previous_Year_PU_Demand_Analysis.xlsx
+++ b/exports/Current_Previous_Year_PU_Demand_Analysis.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Demand SMH Wise - AUG 2026 | up" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PU Staff Current Year - AUG 202" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PU Non Staff Current Year - AUG" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PU Previous Year Comparison - A" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Demand Previous Year Comparison" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Demand SMH Wise - AUG 2026 | up" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="PU Staff Current Year - AUG 202" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="PU Non Staff Current Year - AUG" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="PU Previous Year Comparison - A" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Demand Previous Year Comparison" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -495,7 +495,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Demand SMH Wise - AUG 2026 | uploaded 2026-09-15T16:03:44+05:30</t>
+          <t>Demand SMH Wise - AUG 2026 | uploaded 2026-09-17T21:32:11+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -1292,7 +1292,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PU Staff Current Year - AUG 2026 | uploaded 2026-09-15T16:03:44+05:30</t>
+          <t>PU Staff Current Year - AUG 2026 | uploaded 2026-09-17T21:32:11+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -2537,7 +2537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PU Non Staff Current Year - AUG 2026 | uploaded 2026-09-15T16:03:44+05:30</t>
+          <t>PU Non Staff Current Year - AUG 2026 | uploaded 2026-09-17T21:32:11+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -3785,7 +3785,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PU Previous Year Comparison - AUG 2026 | uploaded 2026-09-15T16:03:44+05:30</t>
+          <t>PU Previous Year Comparison - AUG 2026 | uploaded 2026-09-17T21:32:11+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -6991,7 +6991,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Demand Previous Year Comparison - AUG 2026 | uploaded 2026-09-15T16:03:44+05:30</t>
+          <t>Demand Previous Year Comparison - AUG 2026 | uploaded 2026-09-17T21:32:11+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>

--- a/exports/Current_Previous_Year_PU_Demand_Analysis.xlsx
+++ b/exports/Current_Previous_Year_PU_Demand_Analysis.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Demand SMH Wise - AUG 2026 | up" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PU Staff Current Year - AUG 202" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PU Non Staff Current Year - AUG" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PU Previous Year Comparison - A" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Demand Previous Year Comparison" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Demand SMH Wise - AUG 2026 | up" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="PU Staff Current Year - AUG 202" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="PU Non Staff Current Year - AUG" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="PU Previous Year Comparison - A" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Demand Previous Year Comparison" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/exports/Current_Previous_Year_PU_Demand_Analysis.xlsx
+++ b/exports/Current_Previous_Year_PU_Demand_Analysis.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Demand SMH Wise - AUG 2026 | up" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="PU Staff Current Year - AUG 202" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="PU Non Staff Current Year - AUG" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="PU Previous Year Comparison - A" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Demand Previous Year Comparison" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Demand SMH Wise - AUG 2026 | up" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PU Staff Current Year - AUG 202" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PU Non Staff Current Year - AUG" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PU Previous Year Comparison - A" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Demand Previous Year Comparison" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/exports/Current_Previous_Year_PU_Demand_Analysis.xlsx
+++ b/exports/Current_Previous_Year_PU_Demand_Analysis.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Demand SMH Wise - AUG 2026 | up" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="PU Staff Current Year - AUG 202" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="PU Non Staff Current Year - AUG" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="PU Previous Year Comparison - A" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Demand Previous Year Comparison" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Demand SMH Wise - AUG 2026 | up" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PU Staff Current Year - AUG 202" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PU Non Staff Current Year - AUG" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PU Previous Year Comparison - A" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Demand Previous Year Comparison" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -495,7 +495,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Demand SMH Wise - AUG 2026 | uploaded 2026-09-25T10:56:20+05:30</t>
+          <t>Demand SMH Wise - AUG 2026 | uploaded 2026-09-29T13:48:08+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -2397,7 +2397,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PU Staff Current Year - AUG 2026 | uploaded 2026-09-25T10:56:20+05:30</t>
+          <t>PU Staff Current Year - AUG 2026 | uploaded 2026-09-29T13:48:08+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -5682,7 +5682,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PU Non Staff Current Year - AUG 2026 | uploaded 2026-09-25T10:56:20+05:30</t>
+          <t>PU Non Staff Current Year - AUG 2026 | uploaded 2026-09-29T13:48:08+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -8970,7 +8970,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PU Previous Year Comparison - AUG 2026 | uploaded 2026-09-25T10:56:20+05:30</t>
+          <t>PU Previous Year Comparison - AUG 2026 | uploaded 2026-09-29T13:48:08+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -18568,7 +18568,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Demand Previous Year Comparison - AUG 2026 | uploaded 2026-09-25T10:56:20+05:30</t>
+          <t>Demand Previous Year Comparison - AUG 2026 | uploaded 2026-09-29T13:48:08+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>

--- a/exports/Current_Previous_Year_PU_Demand_Analysis.xlsx
+++ b/exports/Current_Previous_Year_PU_Demand_Analysis.xlsx
@@ -495,7 +495,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Demand SMH Wise - SEP 2026 | uploaded 2026-10-01T11:01:41+05:30</t>
+          <t>Demand SMH Wise - SEP 2026 | uploaded 2026-10-05T14:47:35+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -656,19 +656,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>350,760</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>35.08 Cr</t>
+            <t>353,512</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>35.35 Cr</t>
           </r>
         </is>
       </c>
@@ -679,25 +679,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>29,999</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>3.00 Cr</t>
+            <t>32,751</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>3.28 Cr</t>
           </r>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>110</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
@@ -707,19 +707,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>290,762</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>29.08 Cr</t>
+            <t>288,010</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>28.80 Cr</t>
           </r>
         </is>
       </c>
@@ -793,19 +793,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>2,122,627</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>212.26 Cr</t>
+            <t>2,126,374</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>212.64 Cr</t>
           </r>
         </is>
       </c>
@@ -816,19 +816,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>318,176</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>31.82 Cr</t>
+            <t>321,923</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>32.19 Cr</t>
           </r>
         </is>
       </c>
@@ -844,19 +844,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>1,486,275</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>148.63 Cr</t>
+            <t>1,482,528</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>148.25 Cr</t>
           </r>
         </is>
       </c>
@@ -1067,19 +1067,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>1,015,079</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>101.51 Cr</t>
+            <t>1,050,104</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>105.01 Cr</t>
           </r>
         </is>
       </c>
@@ -1090,25 +1090,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>338,288</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>33.83 Cr</t>
+            <t>373,314</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>37.33 Cr</t>
           </r>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>155</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
@@ -1118,25 +1118,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>338,502</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>33.85 Cr</t>
+            <t>303,477</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>30.35 Cr</t>
           </r>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>78</t>
         </is>
       </c>
     </row>
@@ -1204,19 +1204,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>1,163,224</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>116.32 Cr</t>
+            <t>1,192,410</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>119.24 Cr</t>
           </r>
         </is>
       </c>
@@ -1227,25 +1227,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>133,249</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>13.32 Cr</t>
+            <t>162,435</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>16.24 Cr</t>
           </r>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>116</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
@@ -1255,25 +1255,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>896,726</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>89.67 Cr</t>
+            <t>867,540</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>86.75 Cr</t>
           </r>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>58</t>
         </is>
       </c>
     </row>
@@ -1341,19 +1341,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>2,316,412</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>231.64 Cr</t>
+            <t>2,344,788</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>234.48 Cr</t>
           </r>
         </is>
       </c>
@@ -1364,25 +1364,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>640,129</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>64.01 Cr</t>
+            <t>668,505</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>66.85 Cr</t>
           </r>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>140</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
@@ -1392,25 +1392,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>1,036,154</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>103.62 Cr</t>
+            <t>1,007,778</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>100.78 Cr</t>
           </r>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>70</t>
         </is>
       </c>
     </row>
@@ -1478,19 +1478,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>2,600,978</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>260.10 Cr</t>
+            <t>2,602,601</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>260.26 Cr</t>
           </r>
         </is>
       </c>
@@ -1501,25 +1501,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>386,595</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>38.66 Cr</t>
+            <t>388,218</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>38.82 Cr</t>
           </r>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>118</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
@@ -1529,19 +1529,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>1,827,788</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>182.78 Cr</t>
+            <t>1,826,165</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>182.62 Cr</t>
           </r>
         </is>
       </c>
@@ -1615,19 +1615,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>5,756,378</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>575.64 Cr</t>
+            <t>7,243,570</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>724.36 Cr</t>
           </r>
         </is>
       </c>
@@ -1638,25 +1638,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-47,225</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-4.72 Cr</t>
+            <t>1,439,967</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>144.00 Cr</t>
           </r>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>125</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
@@ -1666,25 +1666,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>5,850,828</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>585.08 Cr</t>
+            <t>4,363,636</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>436.36 Cr</t>
           </r>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>62</t>
         </is>
       </c>
     </row>
@@ -1752,19 +1752,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>1,052,451</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>105.25 Cr</t>
+            <t>1,053,707</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>105.37 Cr</t>
           </r>
         </is>
       </c>
@@ -1775,19 +1775,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>356,035</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>35.60 Cr</t>
+            <t>357,291</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>35.73 Cr</t>
           </r>
         </is>
       </c>
@@ -1803,19 +1803,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>340,381</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>34.04 Cr</t>
+            <t>339,125</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>33.91 Cr</t>
           </r>
         </is>
       </c>
@@ -1889,19 +1889,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>528,378</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>52.84 Cr</t>
+            <t>529,510</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>52.95 Cr</t>
           </r>
         </is>
       </c>
@@ -1912,19 +1912,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>31,059</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>3.11 Cr</t>
+            <t>32,191</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>3.22 Cr</t>
           </r>
         </is>
       </c>
@@ -1940,19 +1940,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>466,260</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>46.63 Cr</t>
+            <t>465,128</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>46.51 Cr</t>
           </r>
         </is>
       </c>
@@ -2159,19 +2159,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>18,328,032</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>1832.80 Cr</t>
+            <t>19,918,321</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>1991.83 Cr</t>
           </r>
         </is>
       </c>
@@ -2182,25 +2182,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>2,030,096</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>203.01 Cr</t>
+            <t>3,620,384</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>362.04 Cr</t>
           </r>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>122</t>
         </is>
       </c>
       <c r="H16" s="5" t="inlineStr">
@@ -2210,25 +2210,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>14,267,841</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>1426.78 Cr</t>
+            <t>12,677,552</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>1267.76 Cr</t>
           </r>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>61</t>
         </is>
       </c>
     </row>
@@ -2296,19 +2296,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>1,591,631</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>159.16 Cr</t>
+            <t>1,591,127</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>159.11 Cr</t>
           </r>
         </is>
       </c>
@@ -2319,25 +2319,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>1,598,154</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>159.82 Cr</t>
+            <t>1,597,650</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>159.76 Cr</t>
           </r>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>-24402</t>
+          <t>-24394</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
@@ -2347,25 +2347,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-1,604,676</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-160.47 Cr</t>
+            <t>-1,604,172</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-160.42 Cr</t>
           </r>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>-12201</t>
+          <t>-12197</t>
         </is>
       </c>
     </row>
@@ -2397,7 +2397,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PU Staff Current Year - SEP 2026 | uploaded 2026-10-01T11:01:41+05:30</t>
+          <t>PU Staff Current Year - SEP 2026 | uploaded 2026-10-05T14:47:35+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -2545,19 +2545,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>3,689,447</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>368.94 Cr</t>
+            <t>3,689,125</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>368.91 Cr</t>
           </r>
         </is>
       </c>
@@ -2568,19 +2568,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>336,242</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>33.62 Cr</t>
+            <t>335,920</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>33.59 Cr</t>
           </r>
         </is>
       </c>
@@ -2596,19 +2596,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>3,016,962</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>301.70 Cr</t>
+            <t>3,017,284</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>301.73 Cr</t>
           </r>
         </is>
       </c>
@@ -2677,19 +2677,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>2,354,387</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>235.44 Cr</t>
+            <t>2,354,304</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>235.43 Cr</t>
           </r>
         </is>
       </c>
@@ -2700,19 +2700,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>304,160</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>30.42 Cr</t>
+            <t>304,078</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>30.41 Cr</t>
           </r>
         </is>
       </c>
@@ -2728,7 +2728,7 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>1,746,066</t>
+            <t>1,746,149</t>
           </r>
           <r>
             <t>
@@ -2941,7 +2941,7 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>405,401</t>
+            <t>405,373</t>
           </r>
           <r>
             <t>
@@ -2964,7 +2964,7 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>17,302</t>
+            <t>17,274</t>
           </r>
           <r>
             <t>
@@ -2992,7 +2992,7 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>370,797</t>
+            <t>370,825</t>
           </r>
           <r>
             <t>
@@ -3073,7 +3073,7 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>259,448</t>
+            <t>259,437</t>
           </r>
           <r>
             <t>
@@ -3096,7 +3096,7 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>11,144</t>
+            <t>11,132</t>
           </r>
           <r>
             <t>
@@ -3124,7 +3124,7 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>237,161</t>
+            <t>237,172</t>
           </r>
           <r>
             <t>
@@ -3337,7 +3337,7 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>437,059</t>
+            <t>437,090</t>
           </r>
           <r>
             <t>
@@ -3360,7 +3360,7 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>96,960</t>
+            <t>96,992</t>
           </r>
           <r>
             <t>
@@ -3388,7 +3388,7 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>243,138</t>
+            <t>243,107</t>
           </r>
           <r>
             <t>
@@ -3601,19 +3601,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>147,747</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>14.77 Cr</t>
+            <t>147,751</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>14.78 Cr</t>
           </r>
         </is>
       </c>
@@ -3624,7 +3624,7 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>42,790</t>
+            <t>42,794</t>
           </r>
           <r>
             <t>
@@ -3652,7 +3652,7 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>62,166</t>
+            <t>62,162</t>
           </r>
           <r>
             <t>
@@ -3733,7 +3733,7 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>318,467</t>
+            <t>318,453</t>
           </r>
           <r>
             <t>
@@ -3756,19 +3756,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>54,551</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>5.46 Cr</t>
+            <t>54,537</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>5.45 Cr</t>
           </r>
         </is>
       </c>
@@ -3784,7 +3784,7 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>209,365</t>
+            <t>209,379</t>
           </r>
           <r>
             <t>
@@ -4129,7 +4129,7 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>265,202</t>
+            <t>265,224</t>
           </r>
           <r>
             <t>
@@ -4152,7 +4152,7 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>111,162</t>
+            <t>111,184</t>
           </r>
           <r>
             <t>
@@ -4180,7 +4180,7 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>42,879</t>
+            <t>42,857</t>
           </r>
           <r>
             <t>
@@ -4393,7 +4393,7 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>16,103</t>
+            <t>16,079</t>
           </r>
           <r>
             <t>
@@ -4416,7 +4416,7 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>6,792</t>
+            <t>6,768</t>
           </r>
           <r>
             <t>
@@ -4444,7 +4444,7 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>2,520</t>
+            <t>2,544</t>
           </r>
           <r>
             <t>
@@ -4657,19 +4657,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>196,466</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>19.65 Cr</t>
+            <t>196,798</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>19.68 Cr</t>
           </r>
         </is>
       </c>
@@ -4680,19 +4680,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>4,270</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>0.43 Cr</t>
+            <t>4,602</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.46 Cr</t>
           </r>
         </is>
       </c>
@@ -4708,19 +4708,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>187,926</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>18.79 Cr</t>
+            <t>187,594</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>18.76 Cr</t>
           </r>
         </is>
       </c>
@@ -5581,19 +5581,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>9,422,907</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>942.29 Cr</t>
+            <t>9,422,814</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>942.28 Cr</t>
           </r>
         </is>
       </c>
@@ -5604,7 +5604,7 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>1,269,147</t>
+            <t>1,269,054</t>
           </r>
           <r>
             <t>
@@ -5632,19 +5632,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>6,884,613</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>688.46 Cr</t>
+            <t>6,884,706</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>688.47 Cr</t>
           </r>
         </is>
       </c>
@@ -5675,14 +5675,14 @@
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PU Non Staff Current Year - SEP 2026 | uploaded 2026-10-01T11:01:41+05:30</t>
+          <t>PU Non Staff Current Year - SEP 2026 | uploaded 2026-10-05T14:47:35+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -6622,19 +6622,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>862,766</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>86.28 Cr</t>
+            <t>1,005,406</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>100.54 Cr</t>
           </r>
         </is>
       </c>
@@ -6645,25 +6645,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>328,390</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>32.84 Cr</t>
+            <t>471,030</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>47.10 Cr</t>
           </r>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>188</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -6673,25 +6673,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>205,986</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>20.60 Cr</t>
+            <t>63,346</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>6.33 Cr</t>
           </r>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>94</t>
         </is>
       </c>
     </row>
@@ -6754,19 +6754,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>79,644</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>7.96 Cr</t>
+            <t>84,936</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>8.49 Cr</t>
           </r>
         </is>
       </c>
@@ -6777,25 +6777,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>4,670</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>0.47 Cr</t>
+            <t>9,962</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>1.00 Cr</t>
           </r>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>113</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
@@ -6805,25 +6805,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>70,303</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>7.03 Cr</t>
+            <t>65,011</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>6.50 Cr</t>
           </r>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>57</t>
         </is>
       </c>
     </row>
@@ -6886,19 +6886,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>2,011,062</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>201.11 Cr</t>
+            <t>2,320,788</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>232.08 Cr</t>
           </r>
         </is>
       </c>
@@ -6909,25 +6909,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>71,700</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>7.17 Cr</t>
+            <t>381,426</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>38.14 Cr</t>
           </r>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>120</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
@@ -6937,25 +6937,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>1,867,662</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>186.77 Cr</t>
+            <t>1,557,936</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>155.79 Cr</t>
           </r>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>60</t>
         </is>
       </c>
     </row>
@@ -7018,19 +7018,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>81,703</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>8.17 Cr</t>
+            <t>102,363</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>10.24 Cr</t>
           </r>
         </is>
       </c>
@@ -7041,25 +7041,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>34,066</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>3.41 Cr</t>
+            <t>54,726</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>5.47 Cr</t>
           </r>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>215</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
@@ -7069,25 +7069,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>13,570</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>1.36 Cr</t>
+            <t>-7,090</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-0.71 Cr</t>
           </r>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>107</t>
         </is>
       </c>
     </row>
@@ -7150,19 +7150,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>2,013,588</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>201.36 Cr</t>
+            <t>2,025,688</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>202.57 Cr</t>
           </r>
         </is>
       </c>
@@ -7173,19 +7173,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>386,433</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>38.64 Cr</t>
+            <t>398,533</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>39.85 Cr</t>
           </r>
         </is>
       </c>
@@ -7201,19 +7201,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>1,240,722</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>124.07 Cr</t>
+            <t>1,228,622</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>122.86 Cr</t>
           </r>
         </is>
       </c>
@@ -7282,19 +7282,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>834,970</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>83.50 Cr</t>
+            <t>1,229,411</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>122.94 Cr</t>
           </r>
         </is>
       </c>
@@ -7305,25 +7305,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-477,750</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-47.77 Cr</t>
+            <t>-83,309</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-8.33 Cr</t>
           </r>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>94</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
@@ -7333,25 +7333,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>1,790,470</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>179.05 Cr</t>
+            <t>1,396,029</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>139.60 Cr</t>
           </r>
         </is>
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>47</t>
         </is>
       </c>
     </row>
@@ -7414,19 +7414,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>23,732</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>2.37 Cr</t>
+            <t>30,063</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>3.01 Cr</t>
           </r>
         </is>
       </c>
@@ -7437,25 +7437,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-54,042</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-5.40 Cr</t>
+            <t>-47,711</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-4.77 Cr</t>
           </r>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>39</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -7465,25 +7465,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>131,816</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>13.18 Cr</t>
+            <t>125,485</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>12.55 Cr</t>
           </r>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -7546,19 +7546,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>56,334</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>5.63 Cr</t>
+            <t>72,149</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>7.21 Cr</t>
           </r>
         </is>
       </c>
@@ -7569,25 +7569,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>8,420</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>0.84 Cr</t>
+            <t>24,234</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>2.42 Cr</t>
           </r>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>151</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
@@ -7597,25 +7597,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>39,495</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>3.95 Cr</t>
+            <t>23,680</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>2.37 Cr</t>
           </r>
         </is>
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>75</t>
         </is>
       </c>
     </row>
@@ -7942,19 +7942,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>2,715,415</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>271.54 Cr</t>
+            <t>3,395,738</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>339.57 Cr</t>
           </r>
         </is>
       </c>
@@ -7965,25 +7965,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>363,737</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>36.37 Cr</t>
+            <t>1,044,060</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>104.41 Cr</t>
           </r>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>144</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
@@ -7993,25 +7993,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>1,987,941</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>198.79 Cr</t>
+            <t>1,307,618</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>130.76 Cr</t>
           </r>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>72</t>
         </is>
       </c>
     </row>
@@ -8074,19 +8074,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>44,502</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>4.45 Cr</t>
+            <t>44,568</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>4.46 Cr</t>
           </r>
         </is>
       </c>
@@ -8097,25 +8097,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>28,338</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>2.83 Cr</t>
+            <t>28,404</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>2.84 Cr</t>
           </r>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>276</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
@@ -8125,7 +8125,7 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-12,173</t>
+            <t>-12,239</t>
           </r>
           <r>
             <t>
@@ -8206,19 +8206,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>44,502</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>4.45 Cr</t>
+            <t>44,568</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>4.46 Cr</t>
           </r>
         </is>
       </c>
@@ -8229,19 +8229,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>28,536</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>2.85 Cr</t>
+            <t>28,602</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>2.86 Cr</t>
           </r>
         </is>
       </c>
@@ -8257,7 +8257,7 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-12,570</t>
+            <t>-12,636</t>
           </r>
           <r>
             <t>
@@ -8275,7 +8275,7 @@
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>140</t>
         </is>
       </c>
     </row>
@@ -8470,19 +8470,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>47,855</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>4.79 Cr</t>
+            <t>48,353</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>4.84 Cr</t>
           </r>
         </is>
       </c>
@@ -8493,25 +8493,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>34,806</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>3.48 Cr</t>
+            <t>35,304</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>3.53 Cr</t>
           </r>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>371</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
@@ -8521,25 +8521,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-21,757</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-2.18 Cr</t>
+            <t>-22,255</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-2.23 Cr</t>
           </r>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>185</t>
         </is>
       </c>
     </row>
@@ -8602,19 +8602,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-652,755</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-65.28 Cr</t>
+            <t>-675,020</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-67.50 Cr</t>
           </r>
         </is>
       </c>
@@ -8625,25 +8625,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>173,656</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>17.37 Cr</t>
+            <t>151,390</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>15.14 Cr</t>
           </r>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>82</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
@@ -8653,25 +8653,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-1,000,066</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-100.01 Cr</t>
+            <t>-977,801</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-97.78 Cr</t>
           </r>
         </is>
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>41</t>
         </is>
       </c>
     </row>
@@ -8734,19 +8734,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>2,323,017</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>232.30 Cr</t>
+            <t>2,347,202</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>234.72 Cr</t>
           </r>
         </is>
       </c>
@@ -8757,25 +8757,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>1,424,228</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>142.42 Cr</t>
+            <t>1,448,412</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>144.84 Cr</t>
           </r>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>261</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
@@ -8785,25 +8785,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-525,438</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-52.54 Cr</t>
+            <t>-549,623</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-54.96 Cr</t>
           </r>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>131</t>
         </is>
       </c>
     </row>
@@ -8866,19 +8866,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>10,496,755</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>1049.68 Cr</t>
+            <t>12,086,633</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>1208.66 Cr</t>
           </r>
         </is>
       </c>
@@ -8889,25 +8889,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>2,359,101</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>235.91 Cr</t>
+            <t>3,948,979</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>394.90 Cr</t>
           </r>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>149</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
@@ -8917,25 +8917,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>5,778,553</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>577.86 Cr</t>
+            <t>4,188,675</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>418.87 Cr</t>
           </r>
         </is>
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>74</t>
         </is>
       </c>
     </row>
@@ -8963,14 +8963,14 @@
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PU Previous Year Comparison - SEP 2026 | uploaded 2026-10-01T11:01:41+05:30</t>
+          <t>PU Previous Year Comparison - SEP 2026 | uploaded 2026-10-05T14:47:35+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -9217,19 +9217,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>3,689,447</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>368.94 Cr</t>
+            <t>3,689,125</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>368.91 Cr</t>
           </r>
         </is>
       </c>
@@ -9240,19 +9240,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>336,242</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>33.62 Cr</t>
+            <t>335,920</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>33.59 Cr</t>
           </r>
         </is>
       </c>
@@ -9268,19 +9268,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>41,949</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>4.19 Cr</t>
+            <t>41,627</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>4.16 Cr</t>
           </r>
         </is>
       </c>
@@ -9418,19 +9418,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>2,354,387</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>235.44 Cr</t>
+            <t>2,354,304</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>235.43 Cr</t>
           </r>
         </is>
       </c>
@@ -9441,19 +9441,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>304,160</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>30.42 Cr</t>
+            <t>304,078</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>30.41 Cr</t>
           </r>
         </is>
       </c>
@@ -9469,19 +9469,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>213,027</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>21.30 Cr</t>
+            <t>212,944</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>21.29 Cr</t>
           </r>
         </is>
       </c>
@@ -9820,7 +9820,7 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>405,401</t>
+            <t>405,373</t>
           </r>
           <r>
             <t>
@@ -9843,7 +9843,7 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>17,302</t>
+            <t>17,274</t>
           </r>
           <r>
             <t>
@@ -9871,7 +9871,7 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>6,198</t>
+            <t>6,170</t>
           </r>
           <r>
             <t>
@@ -10021,7 +10021,7 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>259,448</t>
+            <t>259,437</t>
           </r>
           <r>
             <t>
@@ -10044,7 +10044,7 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>11,144</t>
+            <t>11,132</t>
           </r>
           <r>
             <t>
@@ -10072,7 +10072,7 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>7,991</t>
+            <t>7,980</t>
           </r>
           <r>
             <t>
@@ -10423,7 +10423,7 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>437,059</t>
+            <t>437,090</t>
           </r>
           <r>
             <t>
@@ -10446,7 +10446,7 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>96,960</t>
+            <t>96,992</t>
           </r>
           <r>
             <t>
@@ -10474,19 +10474,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>42,934</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>4.29 Cr</t>
+            <t>42,965</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>4.30 Cr</t>
           </r>
         </is>
       </c>
@@ -10825,19 +10825,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>147,747</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>14.77 Cr</t>
+            <t>147,751</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>14.78 Cr</t>
           </r>
         </is>
       </c>
@@ -10848,7 +10848,7 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>42,790</t>
+            <t>42,794</t>
           </r>
           <r>
             <t>
@@ -10876,7 +10876,7 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>5,699</t>
+            <t>5,703</t>
           </r>
           <r>
             <t>
@@ -11026,7 +11026,7 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>318,467</t>
+            <t>318,453</t>
           </r>
           <r>
             <t>
@@ -11049,19 +11049,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>54,551</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>5.46 Cr</t>
+            <t>54,537</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>5.45 Cr</t>
           </r>
         </is>
       </c>
@@ -11077,7 +11077,7 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>1,771</t>
+            <t>1,757</t>
           </r>
           <r>
             <t>
@@ -11629,7 +11629,7 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>265,202</t>
+            <t>265,224</t>
           </r>
           <r>
             <t>
@@ -11652,7 +11652,7 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>111,162</t>
+            <t>111,184</t>
           </r>
           <r>
             <t>
@@ -11680,7 +11680,7 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>5,716</t>
+            <t>5,738</t>
           </r>
           <r>
             <t>
@@ -12433,7 +12433,7 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>16,103</t>
+            <t>16,079</t>
           </r>
           <r>
             <t>
@@ -12456,7 +12456,7 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>6,792</t>
+            <t>6,768</t>
           </r>
           <r>
             <t>
@@ -12484,7 +12484,7 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>5,930</t>
+            <t>5,906</t>
           </r>
           <r>
             <t>
@@ -13639,19 +13639,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>196,466</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>19.65 Cr</t>
+            <t>196,798</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>19.68 Cr</t>
           </r>
         </is>
       </c>
@@ -13662,19 +13662,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>4,270</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>0.43 Cr</t>
+            <t>4,602</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.46 Cr</t>
           </r>
         </is>
       </c>
@@ -13690,19 +13690,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>9,011</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>0.90 Cr</t>
+            <t>9,343</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.93 Cr</t>
           </r>
         </is>
       </c>
@@ -13840,19 +13840,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>862,766</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>86.28 Cr</t>
+            <t>1,005,406</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>100.54 Cr</t>
           </r>
         </is>
       </c>
@@ -13863,25 +13863,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>328,390</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>32.84 Cr</t>
+            <t>471,030</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>47.10 Cr</t>
           </r>
         </is>
       </c>
       <c r="I28" s="5" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>188</t>
         </is>
       </c>
       <c r="J28" s="5" t="inlineStr">
@@ -13891,25 +13891,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>211,119</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>21.11 Cr</t>
+            <t>353,759</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>35.38 Cr</t>
           </r>
         </is>
       </c>
       <c r="K28" s="5" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>94</t>
         </is>
       </c>
     </row>
@@ -14041,19 +14041,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>79,644</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>7.96 Cr</t>
+            <t>84,936</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>8.49 Cr</t>
           </r>
         </is>
       </c>
@@ -14064,25 +14064,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>4,670</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>0.47 Cr</t>
+            <t>9,962</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>1.00 Cr</t>
           </r>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>113</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
@@ -14092,25 +14092,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-39,591</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-3.96 Cr</t>
+            <t>-34,299</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-3.43 Cr</t>
           </r>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>57</t>
         </is>
       </c>
     </row>
@@ -14443,19 +14443,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>2,011,062</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>201.11 Cr</t>
+            <t>2,320,788</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>232.08 Cr</t>
           </r>
         </is>
       </c>
@@ -14466,25 +14466,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>71,700</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>7.17 Cr</t>
+            <t>381,426</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>38.14 Cr</t>
           </r>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>120</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
@@ -14494,25 +14494,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>30,418</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>3.04 Cr</t>
+            <t>340,144</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>34.01 Cr</t>
           </r>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>60</t>
         </is>
       </c>
     </row>
@@ -14644,19 +14644,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>81,703</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>8.17 Cr</t>
+            <t>102,363</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>10.24 Cr</t>
           </r>
         </is>
       </c>
@@ -14667,25 +14667,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>34,066</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>3.41 Cr</t>
+            <t>54,726</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>5.47 Cr</t>
           </r>
         </is>
       </c>
       <c r="I32" s="5" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>215</t>
         </is>
       </c>
       <c r="J32" s="5" t="inlineStr">
@@ -14695,25 +14695,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>45,643</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>4.56 Cr</t>
+            <t>66,303</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>6.63 Cr</t>
           </r>
         </is>
       </c>
       <c r="K32" s="5" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>107</t>
         </is>
       </c>
     </row>
@@ -14845,19 +14845,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>2,013,588</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>201.36 Cr</t>
+            <t>2,025,688</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>202.57 Cr</t>
           </r>
         </is>
       </c>
@@ -14868,19 +14868,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>386,433</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>38.64 Cr</t>
+            <t>398,533</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>39.85 Cr</t>
           </r>
         </is>
       </c>
@@ -14896,19 +14896,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>178,435</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>17.84 Cr</t>
+            <t>190,535</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>19.05 Cr</t>
           </r>
         </is>
       </c>
@@ -15046,19 +15046,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>834,970</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>83.50 Cr</t>
+            <t>1,229,411</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>122.94 Cr</t>
           </r>
         </is>
       </c>
@@ -15069,25 +15069,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-477,750</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-47.77 Cr</t>
+            <t>-83,309</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-8.33 Cr</t>
           </r>
         </is>
       </c>
       <c r="I34" s="5" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>94</t>
         </is>
       </c>
       <c r="J34" s="5" t="inlineStr">
@@ -15097,25 +15097,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-608,347</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-60.83 Cr</t>
+            <t>-213,906</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-21.39 Cr</t>
           </r>
         </is>
       </c>
       <c r="K34" s="5" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>47</t>
         </is>
       </c>
     </row>
@@ -15247,19 +15247,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>23,732</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>2.37 Cr</t>
+            <t>30,063</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>3.01 Cr</t>
           </r>
         </is>
       </c>
@@ -15270,25 +15270,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-54,042</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-5.40 Cr</t>
+            <t>-47,711</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-4.77 Cr</t>
           </r>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>39</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
@@ -15298,25 +15298,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-59,864</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-5.99 Cr</t>
+            <t>-53,533</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-5.35 Cr</t>
           </r>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -15448,19 +15448,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>56,334</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>5.63 Cr</t>
+            <t>72,149</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>7.21 Cr</t>
           </r>
         </is>
       </c>
@@ -15471,25 +15471,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>8,420</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>0.84 Cr</t>
+            <t>24,234</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>2.42 Cr</t>
           </r>
         </is>
       </c>
       <c r="I36" s="5" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>151</t>
         </is>
       </c>
       <c r="J36" s="5" t="inlineStr">
@@ -15499,25 +15499,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-4,650</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-0.47 Cr</t>
+            <t>11,165</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>1.12 Cr</t>
           </r>
         </is>
       </c>
       <c r="K36" s="5" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>75</t>
         </is>
       </c>
     </row>
@@ -17056,19 +17056,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>2,715,415</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>271.54 Cr</t>
+            <t>3,395,738</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>339.57 Cr</t>
           </r>
         </is>
       </c>
@@ -17079,25 +17079,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>363,737</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>36.37 Cr</t>
+            <t>1,044,060</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>104.41 Cr</t>
           </r>
         </is>
       </c>
       <c r="I44" s="5" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>144</t>
         </is>
       </c>
       <c r="J44" s="5" t="inlineStr">
@@ -17107,25 +17107,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>115,662</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>11.57 Cr</t>
+            <t>795,985</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>79.60 Cr</t>
           </r>
         </is>
       </c>
       <c r="K44" s="5" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>72</t>
         </is>
       </c>
     </row>
@@ -17257,19 +17257,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>44,502</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>4.45 Cr</t>
+            <t>44,568</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>4.46 Cr</t>
           </r>
         </is>
       </c>
@@ -17280,25 +17280,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>28,338</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>2.83 Cr</t>
+            <t>28,404</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>2.84 Cr</t>
           </r>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>276</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
@@ -17308,19 +17308,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>33,748</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>3.37 Cr</t>
+            <t>33,814</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>3.38 Cr</t>
           </r>
         </is>
       </c>
@@ -17458,19 +17458,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>44,502</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>4.45 Cr</t>
+            <t>44,568</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>4.46 Cr</t>
           </r>
         </is>
       </c>
@@ -17481,19 +17481,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>28,536</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>2.85 Cr</t>
+            <t>28,602</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>2.86 Cr</t>
           </r>
         </is>
       </c>
@@ -17509,25 +17509,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>33,749</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>3.37 Cr</t>
+            <t>33,815</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>3.38 Cr</t>
           </r>
         </is>
       </c>
       <c r="K46" s="5" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>140</t>
         </is>
       </c>
     </row>
@@ -17860,19 +17860,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>47,855</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>4.79 Cr</t>
+            <t>48,353</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>4.84 Cr</t>
           </r>
         </is>
       </c>
@@ -17883,25 +17883,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>34,806</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>3.48 Cr</t>
+            <t>35,304</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>3.53 Cr</t>
           </r>
         </is>
       </c>
       <c r="I48" s="5" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>371</t>
         </is>
       </c>
       <c r="J48" s="5" t="inlineStr">
@@ -17911,25 +17911,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>35,645</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>3.56 Cr</t>
+            <t>36,143</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>3.61 Cr</t>
           </r>
         </is>
       </c>
       <c r="K48" s="5" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>185</t>
         </is>
       </c>
     </row>
@@ -18061,19 +18061,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-652,755</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-65.28 Cr</t>
+            <t>-675,020</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-67.50 Cr</t>
           </r>
         </is>
       </c>
@@ -18084,25 +18084,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>173,656</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>17.37 Cr</t>
+            <t>151,390</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>15.14 Cr</t>
           </r>
         </is>
       </c>
       <c r="I49" s="3" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>82</t>
         </is>
       </c>
       <c r="J49" s="3" t="inlineStr">
@@ -18112,25 +18112,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-36,151</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-3.62 Cr</t>
+            <t>-58,416</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-5.84 Cr</t>
           </r>
         </is>
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>41</t>
         </is>
       </c>
     </row>
@@ -18262,19 +18262,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>2,323,017</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>232.30 Cr</t>
+            <t>2,347,202</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>234.72 Cr</t>
           </r>
         </is>
       </c>
@@ -18285,25 +18285,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>1,424,228</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>142.42 Cr</t>
+            <t>1,448,412</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>144.84 Cr</t>
           </r>
         </is>
       </c>
       <c r="I50" s="5" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>261</t>
         </is>
       </c>
       <c r="J50" s="5" t="inlineStr">
@@ -18313,25 +18313,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-41,939</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-4.19 Cr</t>
+            <t>-17,754</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-1.78 Cr</t>
           </r>
         </is>
       </c>
       <c r="K50" s="5" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>131</t>
         </is>
       </c>
     </row>
@@ -18463,19 +18463,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>19,919,662</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>1991.97 Cr</t>
+            <t>21,509,447</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>2150.94 Cr</t>
           </r>
         </is>
       </c>
@@ -18486,25 +18486,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>3,628,248</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>362.82 Cr</t>
+            <t>5,218,033</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>521.80 Cr</t>
           </r>
         </is>
       </c>
       <c r="I51" s="3" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>132</t>
         </is>
       </c>
       <c r="J51" s="3" t="inlineStr">
@@ -18514,25 +18514,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>196,670</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>19.67 Cr</t>
+            <t>1,786,455</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>178.65 Cr</t>
           </r>
         </is>
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>66</t>
         </is>
       </c>
     </row>
@@ -18561,14 +18561,14 @@
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Demand Previous Year Comparison - SEP 2026 | uploaded 2026-10-01T11:01:41+05:30</t>
+          <t>Demand Previous Year Comparison - SEP 2026 | uploaded 2026-10-05T14:47:35+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -18828,19 +18828,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>350,760</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>35.08 Cr</t>
+            <t>353,512</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>35.35 Cr</t>
           </r>
         </is>
       </c>
@@ -18851,25 +18851,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>29,999</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>3.00 Cr</t>
+            <t>32,751</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>3.28 Cr</t>
           </r>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>110</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
@@ -18879,19 +18879,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>22,331</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>2.23 Cr</t>
+            <t>25,083</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>2.51 Cr</t>
           </r>
         </is>
       </c>
@@ -19034,19 +19034,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>2,122,627</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>212.26 Cr</t>
+            <t>2,126,374</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>212.64 Cr</t>
           </r>
         </is>
       </c>
@@ -19057,19 +19057,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>318,176</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>31.82 Cr</t>
+            <t>321,923</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>32.19 Cr</t>
           </r>
         </is>
       </c>
@@ -19085,19 +19085,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>89,037</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>8.90 Cr</t>
+            <t>92,784</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>9.28 Cr</t>
           </r>
         </is>
       </c>
@@ -19446,19 +19446,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>1,015,079</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>101.51 Cr</t>
+            <t>1,050,104</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>105.01 Cr</t>
           </r>
         </is>
       </c>
@@ -19469,25 +19469,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>338,288</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>33.83 Cr</t>
+            <t>373,314</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>37.33 Cr</t>
           </r>
         </is>
       </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>155</t>
         </is>
       </c>
       <c r="K8" s="5" t="inlineStr">
@@ -19497,25 +19497,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>212,392</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>21.24 Cr</t>
+            <t>247,417</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>24.74 Cr</t>
           </r>
         </is>
       </c>
       <c r="L8" s="5" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>78</t>
         </is>
       </c>
     </row>
@@ -19652,19 +19652,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>1,163,224</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>116.32 Cr</t>
+            <t>1,192,410</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>119.24 Cr</t>
           </r>
         </is>
       </c>
@@ -19675,25 +19675,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>133,249</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>13.32 Cr</t>
+            <t>162,435</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>16.24 Cr</t>
           </r>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>116</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
@@ -19703,25 +19703,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>68,051</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>6.81 Cr</t>
+            <t>97,237</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>9.72 Cr</t>
           </r>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>58</t>
         </is>
       </c>
     </row>
@@ -19858,19 +19858,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>2,316,412</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>231.64 Cr</t>
+            <t>2,344,788</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>234.48 Cr</t>
           </r>
         </is>
       </c>
@@ -19881,25 +19881,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>640,129</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>64.01 Cr</t>
+            <t>668,505</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>66.85 Cr</t>
           </r>
         </is>
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>140</t>
         </is>
       </c>
       <c r="K10" s="5" t="inlineStr">
@@ -19909,25 +19909,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>404,583</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>40.46 Cr</t>
+            <t>432,959</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>43.30 Cr</t>
           </r>
         </is>
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>70</t>
         </is>
       </c>
     </row>
@@ -20064,19 +20064,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>2,600,978</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>260.10 Cr</t>
+            <t>2,602,601</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>260.26 Cr</t>
           </r>
         </is>
       </c>
@@ -20087,25 +20087,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>386,595</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>38.66 Cr</t>
+            <t>388,218</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>38.82 Cr</t>
           </r>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>118</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
@@ -20115,19 +20115,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>82,591</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>8.26 Cr</t>
+            <t>84,214</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>8.42 Cr</t>
           </r>
         </is>
       </c>
@@ -20270,19 +20270,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>5,756,378</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>575.64 Cr</t>
+            <t>7,243,570</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>724.36 Cr</t>
           </r>
         </is>
       </c>
@@ -20293,25 +20293,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-47,225</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-4.72 Cr</t>
+            <t>1,439,967</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>144.00 Cr</t>
           </r>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>125</t>
         </is>
       </c>
       <c r="K12" s="5" t="inlineStr">
@@ -20321,25 +20321,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-579,229</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-57.92 Cr</t>
+            <t>907,963</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>90.80 Cr</t>
           </r>
         </is>
       </c>
       <c r="L12" s="5" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>62</t>
         </is>
       </c>
     </row>
@@ -20476,19 +20476,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>1,052,451</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>105.25 Cr</t>
+            <t>1,053,707</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>105.37 Cr</t>
           </r>
         </is>
       </c>
@@ -20499,19 +20499,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>356,035</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>35.60 Cr</t>
+            <t>357,291</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>35.73 Cr</t>
           </r>
         </is>
       </c>
@@ -20527,19 +20527,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>110,484</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>11.05 Cr</t>
+            <t>111,740</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>11.17 Cr</t>
           </r>
         </is>
       </c>
@@ -20682,19 +20682,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>528,378</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>52.84 Cr</t>
+            <t>529,510</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>52.95 Cr</t>
           </r>
         </is>
       </c>
@@ -20705,19 +20705,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>31,059</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>3.11 Cr</t>
+            <t>32,191</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>3.22 Cr</t>
           </r>
         </is>
       </c>
@@ -20733,19 +20733,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>35,488</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>3.55 Cr</t>
+            <t>36,620</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>3.66 Cr</t>
           </r>
         </is>
       </c>
@@ -21090,19 +21090,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>18,328,032</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>1832.80 Cr</t>
+            <t>19,918,321</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>1991.83 Cr</t>
           </r>
         </is>
       </c>
@@ -21113,25 +21113,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>2,030,096</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>203.01 Cr</t>
+            <t>3,620,384</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>362.04 Cr</t>
           </r>
         </is>
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>122</t>
         </is>
       </c>
       <c r="K16" s="5" t="inlineStr">
@@ -21141,25 +21141,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>270,466</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>27.05 Cr</t>
+            <t>1,860,755</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>186.08 Cr</t>
           </r>
         </is>
       </c>
       <c r="L16" s="5" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>61</t>
         </is>
       </c>
     </row>
@@ -21296,19 +21296,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>1,591,631</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>159.16 Cr</t>
+            <t>1,591,127</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>159.11 Cr</t>
           </r>
         </is>
       </c>
@@ -21319,25 +21319,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>1,598,154</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>159.82 Cr</t>
+            <t>1,597,650</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>159.76 Cr</t>
           </r>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>-24402</t>
+          <t>-24394</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
@@ -21347,25 +21347,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-73,847</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-7.38 Cr</t>
+            <t>-74,351</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-7.44 Cr</t>
           </r>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>-12201</t>
+          <t>-12197</t>
         </is>
       </c>
     </row>

--- a/exports/Current_Previous_Year_PU_Demand_Analysis.xlsx
+++ b/exports/Current_Previous_Year_PU_Demand_Analysis.xlsx
@@ -495,7 +495,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Demand SMH Wise - SEP 2026 | uploaded 2026-10-05T14:47:35+05:30</t>
+          <t>Demand SMH Wise - SEP 2026 | uploaded 2026-10-06T10:20:58+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -2397,7 +2397,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PU Staff Current Year - SEP 2026 | uploaded 2026-10-05T14:47:35+05:30</t>
+          <t>PU Staff Current Year - SEP 2026 | uploaded 2026-10-06T10:20:58+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -5682,7 +5682,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PU Non Staff Current Year - SEP 2026 | uploaded 2026-10-05T14:47:35+05:30</t>
+          <t>PU Non Staff Current Year - SEP 2026 | uploaded 2026-10-06T10:20:58+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -8970,7 +8970,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PU Previous Year Comparison - SEP 2026 | uploaded 2026-10-05T14:47:35+05:30</t>
+          <t>PU Previous Year Comparison - SEP 2026 | uploaded 2026-10-06T10:20:58+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -18568,7 +18568,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Demand Previous Year Comparison - SEP 2026 | uploaded 2026-10-05T14:47:35+05:30</t>
+          <t>Demand Previous Year Comparison - SEP 2026 | uploaded 2026-10-06T10:20:58+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>

--- a/exports/Current_Previous_Year_PU_Demand_Analysis.xlsx
+++ b/exports/Current_Previous_Year_PU_Demand_Analysis.xlsx
@@ -495,7 +495,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Demand SMH Wise - SEP 2026 | uploaded 2026-10-06T10:20:58+05:30</t>
+          <t>Demand SMH Wise - SEP 2026 | uploaded 2026-10-19T14:05:55+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -2397,7 +2397,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PU Staff Current Year - SEP 2026 | uploaded 2026-10-06T10:20:58+05:30</t>
+          <t>PU Staff Current Year - SEP 2026 | uploaded 2026-10-19T14:05:55+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -5682,7 +5682,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PU Non Staff Current Year - SEP 2026 | uploaded 2026-10-06T10:20:58+05:30</t>
+          <t>PU Non Staff Current Year - SEP 2026 | uploaded 2026-10-19T14:05:55+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -8970,7 +8970,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PU Previous Year Comparison - SEP 2026 | uploaded 2026-10-06T10:20:58+05:30</t>
+          <t>PU Previous Year Comparison - SEP 2026 | uploaded 2026-10-19T14:05:55+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -18568,7 +18568,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Demand Previous Year Comparison - SEP 2026 | uploaded 2026-10-06T10:20:58+05:30</t>
+          <t>Demand Previous Year Comparison - SEP 2026 | uploaded 2026-10-19T14:05:55+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>

--- a/exports/Current_Previous_Year_PU_Demand_Analysis.xlsx
+++ b/exports/Current_Previous_Year_PU_Demand_Analysis.xlsx
@@ -495,7 +495,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Demand SMH Wise - SEP 2026 | uploaded 2026-10-19T14:05:55+05:30</t>
+          <t>Demand SMH Wise - SEP 2026 | uploaded 2026-10-27T11:36:19+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -610,19 +610,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>641,522</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>64.15 Cr</t>
+            <t>643,222</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>64.32 Cr</t>
           </r>
         </is>
       </c>
@@ -633,19 +633,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>320,761</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>32.08 Cr</t>
+            <t>321,611</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>32.16 Cr</t>
           </r>
         </is>
       </c>
@@ -679,19 +679,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>32,751</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>3.28 Cr</t>
+            <t>31,901</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>3.19 Cr</t>
           </r>
         </is>
       </c>
@@ -707,19 +707,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>288,010</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>28.80 Cr</t>
+            <t>289,710</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>28.97 Cr</t>
           </r>
         </is>
       </c>
@@ -747,19 +747,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>3,608,902</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>360.89 Cr</t>
+            <t>3,809,302</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>380.93 Cr</t>
           </r>
         </is>
       </c>
@@ -770,19 +770,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>1,804,451</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>180.45 Cr</t>
+            <t>1,904,651</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>190.47 Cr</t>
           </r>
         </is>
       </c>
@@ -816,25 +816,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>321,923</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>32.19 Cr</t>
+            <t>221,723</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>22.17 Cr</t>
           </r>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>112</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
@@ -844,25 +844,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>1,482,528</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>148.25 Cr</t>
+            <t>1,682,928</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>168.29 Cr</t>
           </r>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>56</t>
         </is>
       </c>
     </row>
@@ -1158,19 +1158,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>2,059,950</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>206.00 Cr</t>
+            <t>2,111,950</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>211.19 Cr</t>
           </r>
         </is>
       </c>
@@ -1181,19 +1181,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>1,029,975</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>103.00 Cr</t>
+            <t>1,055,975</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>105.60 Cr</t>
           </r>
         </is>
       </c>
@@ -1227,25 +1227,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>162,435</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>16.24 Cr</t>
+            <t>136,435</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>13.64 Cr</t>
           </r>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>113</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
@@ -1255,25 +1255,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>867,540</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>86.75 Cr</t>
+            <t>919,540</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>91.95 Cr</t>
           </r>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>56</t>
         </is>
       </c>
     </row>
@@ -1432,19 +1432,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>4,428,766</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>442.88 Cr</t>
+            <t>4,504,666</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>450.47 Cr</t>
           </r>
         </is>
       </c>
@@ -1455,19 +1455,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>2,214,383</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>221.44 Cr</t>
+            <t>2,252,333</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>225.23 Cr</t>
           </r>
         </is>
       </c>
@@ -1501,25 +1501,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>388,218</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>38.82 Cr</t>
+            <t>350,268</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>35.03 Cr</t>
           </r>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>116</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
@@ -1529,25 +1529,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>1,826,165</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>182.62 Cr</t>
+            <t>1,902,065</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>190.21 Cr</t>
           </r>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>58</t>
         </is>
       </c>
     </row>
@@ -2113,19 +2113,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>32,595,873</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>3259.59 Cr</t>
+            <t>32,925,873</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>3292.59 Cr</t>
           </r>
         </is>
       </c>
@@ -2136,19 +2136,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>16,297,936</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>1629.79 Cr</t>
+            <t>16,462,936</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>1646.29 Cr</t>
           </r>
         </is>
       </c>
@@ -2182,25 +2182,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>3,620,384</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>362.04 Cr</t>
+            <t>3,455,384</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>345.54 Cr</t>
           </r>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>121</t>
         </is>
       </c>
       <c r="H16" s="5" t="inlineStr">
@@ -2210,25 +2210,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>12,677,552</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>1267.76 Cr</t>
+            <t>13,007,552</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>1300.76 Cr</t>
           </r>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>60</t>
         </is>
       </c>
     </row>
@@ -2397,7 +2397,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PU Staff Current Year - SEP 2026 | uploaded 2026-10-19T14:05:55+05:30</t>
+          <t>PU Staff Current Year - SEP 2026 | uploaded 2026-10-27T11:36:19+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -5682,7 +5682,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PU Non Staff Current Year - SEP 2026 | uploaded 2026-10-19T14:05:55+05:30</t>
+          <t>PU Non Staff Current Year - SEP 2026 | uploaded 2026-10-27T11:36:19+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -6708,19 +6708,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>149,947</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>14.99 Cr</t>
+            <t>192,347</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>19.23 Cr</t>
           </r>
         </is>
       </c>
@@ -6731,19 +6731,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>74,974</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>7.50 Cr</t>
+            <t>96,174</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>9.62 Cr</t>
           </r>
         </is>
       </c>
@@ -6777,25 +6777,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>9,962</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>1.00 Cr</t>
+            <t>-11,238</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-1.12 Cr</t>
           </r>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>88</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
@@ -6805,25 +6805,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>65,011</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>6.50 Cr</t>
+            <t>107,411</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>10.74 Cr</t>
           </r>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>44</t>
         </is>
       </c>
     </row>
@@ -7104,19 +7104,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>3,254,310</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>325.43 Cr</t>
+            <t>3,541,910</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>354.19 Cr</t>
           </r>
         </is>
       </c>
@@ -7127,19 +7127,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>1,627,155</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>162.72 Cr</t>
+            <t>1,770,955</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>177.10 Cr</t>
           </r>
         </is>
       </c>
@@ -7173,25 +7173,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>398,533</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>39.85 Cr</t>
+            <t>254,733</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>25.47 Cr</t>
           </r>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>114</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -7201,25 +7201,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>1,228,622</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>122.86 Cr</t>
+            <t>1,516,222</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>151.62 Cr</t>
           </r>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>57</t>
         </is>
       </c>
     </row>
@@ -8820,19 +8820,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>16,275,308</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>1627.53 Cr</t>
+            <t>16,605,308</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>1660.53 Cr</t>
           </r>
         </is>
       </c>
@@ -8843,19 +8843,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>8,137,654</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>813.77 Cr</t>
+            <t>8,302,654</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>830.27 Cr</t>
           </r>
         </is>
       </c>
@@ -8889,25 +8889,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>3,948,979</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>394.90 Cr</t>
+            <t>3,783,979</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>378.40 Cr</t>
           </r>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>146</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
@@ -8917,25 +8917,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>4,188,675</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>418.87 Cr</t>
+            <t>4,518,675</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>451.87 Cr</t>
           </r>
         </is>
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>73</t>
         </is>
       </c>
     </row>
@@ -8970,7 +8970,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PU Previous Year Comparison - SEP 2026 | uploaded 2026-10-19T14:05:55+05:30</t>
+          <t>PU Previous Year Comparison - SEP 2026 | uploaded 2026-10-27T11:36:19+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -13995,19 +13995,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>149,947</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>14.99 Cr</t>
+            <t>192,347</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>19.23 Cr</t>
           </r>
         </is>
       </c>
@@ -14018,19 +14018,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>74,974</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>7.50 Cr</t>
+            <t>96,174</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>9.62 Cr</t>
           </r>
         </is>
       </c>
@@ -14064,25 +14064,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>9,962</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>1.00 Cr</t>
+            <t>-11,238</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-1.12 Cr</t>
           </r>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>88</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
@@ -14110,7 +14110,7 @@
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>44</t>
         </is>
       </c>
     </row>
@@ -14799,19 +14799,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>3,254,310</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>325.43 Cr</t>
+            <t>3,541,910</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>354.19 Cr</t>
           </r>
         </is>
       </c>
@@ -14822,19 +14822,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>1,627,155</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>162.72 Cr</t>
+            <t>1,770,955</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>177.10 Cr</t>
           </r>
         </is>
       </c>
@@ -14868,25 +14868,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>398,533</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>39.85 Cr</t>
+            <t>254,733</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>25.47 Cr</t>
           </r>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>114</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
@@ -14914,7 +14914,7 @@
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>57</t>
         </is>
       </c>
     </row>
@@ -18417,19 +18417,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>32,582,828</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>3258.28 Cr</t>
+            <t>32,912,828</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>3291.28 Cr</t>
           </r>
         </is>
       </c>
@@ -18440,19 +18440,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>16,291,414</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>1629.14 Cr</t>
+            <t>16,456,414</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>1645.64 Cr</t>
           </r>
         </is>
       </c>
@@ -18486,25 +18486,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>5,218,033</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>521.80 Cr</t>
+            <t>5,053,033</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>505.30 Cr</t>
           </r>
         </is>
       </c>
       <c r="I51" s="3" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>131</t>
         </is>
       </c>
       <c r="J51" s="3" t="inlineStr">
@@ -18532,7 +18532,7 @@
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>65</t>
         </is>
       </c>
     </row>
@@ -18568,7 +18568,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Demand Previous Year Comparison - SEP 2026 | uploaded 2026-10-19T14:05:55+05:30</t>
+          <t>Demand Previous Year Comparison - SEP 2026 | uploaded 2026-10-27T11:36:19+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -18782,19 +18782,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>641,522</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>64.15 Cr</t>
+            <t>643,222</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>64.32 Cr</t>
           </r>
         </is>
       </c>
@@ -18805,19 +18805,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>320,761</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>32.08 Cr</t>
+            <t>321,611</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>32.16 Cr</t>
           </r>
         </is>
       </c>
@@ -18851,19 +18851,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>32,751</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>3.28 Cr</t>
+            <t>31,901</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>3.19 Cr</t>
           </r>
         </is>
       </c>
@@ -18988,19 +18988,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>3,608,902</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>360.89 Cr</t>
+            <t>3,809,302</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>380.93 Cr</t>
           </r>
         </is>
       </c>
@@ -19011,19 +19011,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>1,804,451</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>180.45 Cr</t>
+            <t>1,904,651</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>190.47 Cr</t>
           </r>
         </is>
       </c>
@@ -19057,25 +19057,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>321,923</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>32.19 Cr</t>
+            <t>221,723</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>22.17 Cr</t>
           </r>
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>112</t>
         </is>
       </c>
       <c r="K6" s="5" t="inlineStr">
@@ -19103,7 +19103,7 @@
       </c>
       <c r="L6" s="5" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>56</t>
         </is>
       </c>
     </row>
@@ -19606,19 +19606,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>2,059,950</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>206.00 Cr</t>
+            <t>2,111,950</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>211.19 Cr</t>
           </r>
         </is>
       </c>
@@ -19629,19 +19629,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>1,029,975</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>103.00 Cr</t>
+            <t>1,055,975</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>105.60 Cr</t>
           </r>
         </is>
       </c>
@@ -19675,25 +19675,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>162,435</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>16.24 Cr</t>
+            <t>136,435</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>13.64 Cr</t>
           </r>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>113</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
@@ -19721,7 +19721,7 @@
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>56</t>
         </is>
       </c>
     </row>
@@ -20018,19 +20018,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>4,428,766</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>442.88 Cr</t>
+            <t>4,504,666</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>450.47 Cr</t>
           </r>
         </is>
       </c>
@@ -20041,19 +20041,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>2,214,383</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>221.44 Cr</t>
+            <t>2,252,333</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>225.23 Cr</t>
           </r>
         </is>
       </c>
@@ -20087,25 +20087,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>388,218</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>38.82 Cr</t>
+            <t>350,268</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>35.03 Cr</t>
           </r>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>116</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
@@ -20133,7 +20133,7 @@
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>58</t>
         </is>
       </c>
     </row>
@@ -21044,19 +21044,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>32,595,873</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>3259.59 Cr</t>
+            <t>32,925,873</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>3292.59 Cr</t>
           </r>
         </is>
       </c>
@@ -21067,19 +21067,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>16,297,936</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>1629.79 Cr</t>
+            <t>16,462,936</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>1646.29 Cr</t>
           </r>
         </is>
       </c>
@@ -21113,25 +21113,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>3,620,384</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>362.04 Cr</t>
+            <t>3,455,384</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>345.54 Cr</t>
           </r>
         </is>
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>121</t>
         </is>
       </c>
       <c r="K16" s="5" t="inlineStr">
@@ -21159,7 +21159,7 @@
       </c>
       <c r="L16" s="5" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>60</t>
         </is>
       </c>
     </row>
